--- a/docs/adr/Benchmark.xlsx
+++ b/docs/adr/Benchmark.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krimi\IPSSI_APOCAL_KIT\docs\cadrage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krimi\IPSSI_APOCAL_KIT\docs\adr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EED5422-FF0F-4622-B921-DA18E0F9F07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8CCEFA-2219-4A45-AC93-BB3ACFCFD4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3360" windowWidth="29040" windowHeight="15720" xr2:uid="{9450BB16-CBD5-4EDD-B402-95B16122CD99}"/>
   </bookViews>
